--- a/data/student.xlsx
+++ b/data/student.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,6 +521,33 @@
       <c r="E4" t="inlineStr">
         <is>
           <t>Demo Lecturer 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TP015826</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Test Student 4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>test04@mail.apu.edu.my</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Demo Lecturer 1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Demo Lecturer 2</t>
         </is>
       </c>
     </row>

--- a/data/student.xlsx
+++ b/data/student.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,108 +446,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TP012345</t>
+          <t>TP083880</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Test Student</t>
+          <t>Yoon</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>test01@mail.apu.edu.my</t>
+          <t>TP083880@mail.apu.edu.my</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Demo Lecturer 1</t>
+          <t>HEMA LATHA A/P KRISHNA NAIR</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Demo Lecturer 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>TP456789</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Test Student 2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>test02@mail.apu.edu.my</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 3</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>TP067890</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Test Student 3</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>test03@mail.apu.edu.my</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 2</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>TP015826</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Test Student 4</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>test04@mail.apu.edu.my</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 1</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 2</t>
+          <t>DR. JULIA BINTI JUREMI</t>
         </is>
       </c>
     </row>
